--- a/Book_previous.xlsx
+++ b/Book_previous.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gelsvalt-my.sharepoint.com/personal/u087_gelsva_lt/Documents/Desktop/python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{369B0C6D-B7E4-40BC-8D03-848E48B3AAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03D3F847-B107-4EEE-A1DC-E3E8F83ECC2E}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{369B0C6D-B7E4-40BC-8D03-848E48B3AAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26E4EAAC-14A9-46DB-8893-0C5A42C510B3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
   <si>
     <t>Produktų skyrius</t>
   </si>
@@ -45,42 +45,9 @@
     <t>Prekės grupė</t>
   </si>
   <si>
-    <t>03MF342</t>
-  </si>
-  <si>
-    <t>4860019002091</t>
-  </si>
-  <si>
-    <t>#Borjomi gāzēts min.ūdens pet 1,25L</t>
-  </si>
-  <si>
-    <t>NON_ALC</t>
-  </si>
-  <si>
-    <t>WATER</t>
-  </si>
-  <si>
-    <t>PET_CARBO</t>
-  </si>
-  <si>
-    <t>03V787445</t>
-  </si>
-  <si>
-    <t>3701172716559</t>
-  </si>
-  <si>
-    <t>Koru Bay Sauvignon Blanc Marlborough baltvīns 0,75L 12,5%</t>
-  </si>
-  <si>
     <t>ALC</t>
   </si>
   <si>
-    <t>WINE</t>
-  </si>
-  <si>
-    <t>WHITE</t>
-  </si>
-  <si>
     <t>Kods</t>
   </si>
   <si>
@@ -145,9 +112,6 @@
   </si>
   <si>
     <t>Iepirkuma cena bez PVN</t>
-  </si>
-  <si>
-    <t>Koru Bay Sauvignon Blanc Marlborough baltvīns 0,75L 13%</t>
   </si>
   <si>
     <t>17.08–23.08.2026</t>
@@ -158,6 +122,39 @@
   </si>
   <si>
     <t>Centra laukums 1, Ezere, Ezeres pagasts, LV-3891</t>
+  </si>
+  <si>
+    <t>69VB2702492</t>
+  </si>
+  <si>
+    <t>8028277000563</t>
+  </si>
+  <si>
+    <t>Chiara Tuncis saulespuķu eļļā 80gx3</t>
+  </si>
+  <si>
+    <t>FOOD</t>
+  </si>
+  <si>
+    <t>FISH</t>
+  </si>
+  <si>
+    <t>PRESERV</t>
+  </si>
+  <si>
+    <t>LV014399</t>
+  </si>
+  <si>
+    <t>4750142004980</t>
+  </si>
+  <si>
+    <t>#Cēsu Premium pint alus can 0,568L 5%</t>
+  </si>
+  <si>
+    <t>BEER</t>
+  </si>
+  <si>
+    <t>BOT_ALE</t>
   </si>
 </sst>
 </file>
@@ -167,7 +164,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\€0.00"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,6 +217,13 @@
       <sz val="11"/>
       <name val="Aptos Narrow"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="186"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -270,7 +274,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -295,6 +299,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -609,13 +616,13 @@
   <sheetData>
     <row r="1" spans="1:21" ht="173.25" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -627,181 +634,179 @@
         <v>2</v>
       </c>
       <c r="G1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="T1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="U1" s="9" t="s">
         <v>19</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q1" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="S1" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="T1" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="U1" s="9" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3">
+        <v>6</v>
+      </c>
+      <c r="J2" s="3">
+        <v>1</v>
+      </c>
+      <c r="K2" s="3">
+        <v>1</v>
+      </c>
+      <c r="L2" s="3">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="M2" s="3">
+        <v>7</v>
+      </c>
+      <c r="N2" s="3">
+        <v>0</v>
+      </c>
+      <c r="O2" s="3">
+        <v>3</v>
+      </c>
+      <c r="P2" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>15</v>
+      </c>
+      <c r="R2" s="3">
+        <v>3</v>
+      </c>
+      <c r="S2" s="3">
         <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="3">
-        <v>9</v>
-      </c>
-      <c r="H2" s="3">
-        <v>13</v>
-      </c>
-      <c r="I2" s="3">
-        <v>16</v>
-      </c>
-      <c r="J2" s="3">
-        <v>16</v>
-      </c>
-      <c r="K2" s="3">
-        <v>18</v>
-      </c>
-      <c r="L2" s="3">
-        <v>31</v>
-      </c>
-      <c r="M2" s="3">
-        <v>55</v>
-      </c>
-      <c r="N2" s="3">
-        <v>6</v>
-      </c>
-      <c r="O2" s="3">
-        <v>22</v>
-      </c>
-      <c r="P2" s="3">
-        <v>25</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>18</v>
-      </c>
-      <c r="R2" s="3">
-        <v>14</v>
-      </c>
-      <c r="S2" s="3">
-        <v>3</v>
       </c>
       <c r="T2" s="3">
         <v>1</v>
       </c>
       <c r="U2" s="3">
-        <f>SUM(G2:T2)</f>
-        <v>247</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="G3" s="3">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="H3" s="3">
-        <v>1</v>
+        <v>133</v>
       </c>
       <c r="I3" s="3">
-        <v>7</v>
+        <v>146</v>
       </c>
       <c r="J3" s="3">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="K3" s="3">
-        <v>1</v>
+        <v>343</v>
       </c>
       <c r="L3" s="3">
-        <v>4</v>
+        <v>892</v>
       </c>
       <c r="M3" s="3">
-        <v>7</v>
+        <v>201</v>
       </c>
       <c r="N3" s="3">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="O3" s="3">
-        <v>2</v>
+        <v>166</v>
       </c>
       <c r="P3" s="3">
-        <v>1</v>
+        <v>111</v>
       </c>
       <c r="Q3" s="3">
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="R3" s="3">
-        <v>3</v>
+        <v>133</v>
       </c>
       <c r="S3" s="3">
-        <v>0</v>
+        <v>347</v>
       </c>
       <c r="T3" s="3">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="U3" s="3">
-        <f>SUM(G3:T3)</f>
-        <v>32</v>
+        <v>3386</v>
       </c>
     </row>
   </sheetData>
@@ -821,52 +826,52 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C1" s="10"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="11">
+        <v>2</v>
+      </c>
+      <c r="C5" s="11">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="11">
-        <v>5.99</v>
-      </c>
-      <c r="C5" s="11">
-        <v>3.0281000000000002</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
       <c r="B6" s="11">
-        <v>2.29</v>
+        <v>0.89</v>
       </c>
       <c r="C6" s="11">
-        <v>1.5109999999999999</v>
+        <v>0.72</v>
       </c>
     </row>
   </sheetData>

--- a/Book_previous.xlsx
+++ b/Book_previous.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gelsvalt-my.sharepoint.com/personal/u087_gelsva_lt/Documents/Desktop/python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{369B0C6D-B7E4-40BC-8D03-848E48B3AAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26E4EAAC-14A9-46DB-8893-0C5A42C510B3}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{369B0C6D-B7E4-40BC-8D03-848E48B3AAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D529B6C6-395B-4B1F-93BD-906660940091}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -84,9 +84,6 @@
     <t>Grostonas iela 1, Vidzemes priekšpilsēta, Rīga, LV-1013</t>
   </si>
   <si>
-    <t>Grenctāles robežkontroles punkts, Brunavas pagasts, Bauskas novads, LV-3907</t>
-  </si>
-  <si>
     <t>Āzenes iela 5, Kurzemes rajons</t>
   </si>
   <si>
@@ -155,6 +152,9 @@
   </si>
   <si>
     <t>BOT_ALE</t>
+  </si>
+  <si>
+    <t>Grenctāle, Robežkontroles punkts, Brunavas pagasts, Bauskas novads, LV-3907</t>
   </si>
 </sst>
 </file>
@@ -614,7 +614,7 @@
     <col min="1" max="8" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="173.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -655,7 +655,7 @@
         <v>13</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O1" s="7" t="s">
         <v>14</v>
@@ -664,39 +664,39 @@
         <v>15</v>
       </c>
       <c r="Q1" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="R1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="S1" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="T1" s="7" t="s">
+      <c r="U1" s="9" t="s">
         <v>18</v>
-      </c>
-      <c r="U1" s="9" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="G2" s="3">
         <v>1</v>
@@ -746,22 +746,22 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="G3" s="3">
         <v>251</v>
@@ -826,35 +826,35 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>20</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>21</v>
       </c>
       <c r="C1" s="10"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="C4" s="10" t="s">
         <v>24</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" s="11">
         <v>2</v>
@@ -865,7 +865,7 @@
     </row>
     <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B6" s="11">
         <v>0.89</v>

--- a/Book_previous.xlsx
+++ b/Book_previous.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gelsvalt-my.sharepoint.com/personal/u087_gelsva_lt/Documents/Desktop/python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{369B0C6D-B7E4-40BC-8D03-848E48B3AAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D529B6C6-395B-4B1F-93BD-906660940091}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{369B0C6D-B7E4-40BC-8D03-848E48B3AAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FD847E1-ADAD-4416-A0A1-BBB71F3A6175}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -111,9 +111,6 @@
     <t>Iepirkuma cena bez PVN</t>
   </si>
   <si>
-    <t>17.08–23.08.2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Biķernieku iela 21, Vidzemes priekšpilsēta, Rīga, LV-1039
 </t>
   </si>
@@ -155,6 +152,9 @@
   </si>
   <si>
     <t>Grenctāle, Robežkontroles punkts, Brunavas pagasts, Bauskas novads, LV-3907</t>
+  </si>
+  <si>
+    <t>10.08–16.08.2026</t>
   </si>
 </sst>
 </file>
@@ -614,7 +614,7 @@
     <col min="1" max="8" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="157.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="173.25" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -655,7 +655,7 @@
         <v>13</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O1" s="7" t="s">
         <v>14</v>
@@ -664,13 +664,13 @@
         <v>15</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R1" s="7" t="s">
         <v>16</v>
       </c>
       <c r="S1" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T1" s="7" t="s">
         <v>17</v>
@@ -681,22 +681,22 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="G2" s="3">
         <v>1</v>
@@ -746,22 +746,22 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="G3" s="3">
         <v>251</v>
@@ -838,7 +838,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -854,10 +854,10 @@
     </row>
     <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" s="11">
-        <v>2</v>
+        <v>4.49</v>
       </c>
       <c r="C5" s="11">
         <v>1.66</v>
@@ -865,10 +865,10 @@
     </row>
     <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" s="11">
-        <v>0.89</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="C6" s="11">
         <v>0.72</v>

--- a/Book_previous.xlsx
+++ b/Book_previous.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{369B0C6D-B7E4-40BC-8D03-848E48B3AAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FD847E1-ADAD-4416-A0A1-BBB71F3A6175}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Book_previous.xlsx
+++ b/Book_previous.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gelsvalt-my.sharepoint.com/personal/u087_gelsva_lt/Documents/Desktop/python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{369B0C6D-B7E4-40BC-8D03-848E48B3AAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FD847E1-ADAD-4416-A0A1-BBB71F3A6175}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="11_455FE02DEA73FC0327D0D3F114FB421ECD3234A9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CB058E2-DB7D-49DE-A53D-544D0901E3DD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Iestatījumi" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$V$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +37,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
+  <si>
+    <t>Kods</t>
+  </si>
+  <si>
+    <t>EAN kods</t>
+  </si>
+  <si>
+    <t>Nosaukums</t>
+  </si>
   <si>
     <t>Produktų skyrius</t>
   </si>
@@ -45,61 +57,73 @@
     <t>Prekės grupė</t>
   </si>
   <si>
+    <t>Latgales iela 400, Latgales priekšpilsēta, Rīga, LV-1063 | 4 nedēļas kopā</t>
+  </si>
+  <si>
+    <t>Vaidavas iela 9B, Vidzemes priekšpilsēta, Rīga, LV-1084 | 4 nedēļas kopā</t>
+  </si>
+  <si>
+    <t>Kalnciema iela 41, Zemgales priekšpilsēta, Rīga, LV-1046 | 4 nedēļas kopā</t>
+  </si>
+  <si>
+    <t>Stirnu iela 26, Vidzemes priekšpilsēta, Rīga, LV-1084 | 4 nedēļas kopā</t>
+  </si>
+  <si>
+    <t>Jomas iela 46, Jūrmala, LV-2015 | 4 nedēļas kopā</t>
+  </si>
+  <si>
+    <t>Lietuvas iela 44, Eleja, Elejas pagasts, LV-3023 | 4 nedēļas kopā</t>
+  </si>
+  <si>
+    <t>Krasta iela 70A, Latgales priekšpilsēta, Rīga, LV-1019 | 4 nedēļas kopā</t>
+  </si>
+  <si>
+    <t>Biķernieku iela 21, Vidzemes priekšpilsēta, Rīga, LV-1039 | 4 nedēļas kopā</t>
+  </si>
+  <si>
+    <t>Brīvības gatve 402C, Vidzemes priekšpilsēta, Rīga, LV-1024 | 4 nedēļas kopā</t>
+  </si>
+  <si>
+    <t>Grostonas iela 1, Vidzemes priekšpilsēta, Rīga, LV-1013 | 4 nedēļas kopā</t>
+  </si>
+  <si>
+    <t>Grenctāle, Robežkontroles punkts, Brunavas pagasts, Bauskas novads, LV-3907 | 4 nedēļas kopā</t>
+  </si>
+  <si>
+    <t>Āzenes iela 5, Kurzemes rajons | 4 nedēļas kopā</t>
+  </si>
+  <si>
+    <t>Centra laukums 1, Ezere, Ezeres pagasts, LV-3891 | 4 nedēļas kopā</t>
+  </si>
+  <si>
+    <t>"Burtnieki", Kalkūnes pagasts, Daugavpils novads, LV-5449 | 4 nedēļas kopā</t>
+  </si>
+  <si>
+    <t>Kopā | 4 nedēļas kopā</t>
+  </si>
+  <si>
+    <t>4 nedēļu vidējais</t>
+  </si>
+  <si>
     <t>ALC</t>
   </si>
   <si>
-    <t>Kods</t>
-  </si>
-  <si>
-    <t>EAN kods</t>
-  </si>
-  <si>
-    <t>Nosaukums</t>
-  </si>
-  <si>
-    <t>Latgales iela 400, Latgales priekšpilsēta, Rīga, LV-1063</t>
-  </si>
-  <si>
-    <t>Vaidavas iela 9B, Vidzemes priekšpilsēta, Rīga, LV-1084</t>
-  </si>
-  <si>
-    <t>Kalnciema iela 41, Zemgales priekšpilsēta, Rīga, LV-1046</t>
-  </si>
-  <si>
-    <t>Stirnu iela 26, Vidzemes priekšpilsēta, Rīga, LV-1084</t>
-  </si>
-  <si>
-    <t>Jomas iela 46, Jūrmala, LV-2015</t>
-  </si>
-  <si>
-    <t>Lietuvas iela 44, Eleja, Elejas pagasts, LV-3023</t>
-  </si>
-  <si>
-    <t>Krasta iela 70A, Latgales priekšpilsēta, Rīga, LV-1019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brīvības gatve 402C, Vidzemes priekšpilsēta, Rīga, LV-1024 </t>
-  </si>
-  <si>
-    <t>Grostonas iela 1, Vidzemes priekšpilsēta, Rīga, LV-1013</t>
-  </si>
-  <si>
-    <t>Āzenes iela 5, Kurzemes rajons</t>
-  </si>
-  <si>
-    <t>"Burtnieki", Kalkūnes pagasts, Daugavpils novads, LV-5449</t>
-  </si>
-  <si>
-    <t>Kopā</t>
-  </si>
-  <si>
     <t>Parametrs</t>
   </si>
   <si>
     <t>Vērtība</t>
   </si>
   <si>
-    <t>Periods</t>
+    <t>Book_previous ievade</t>
+  </si>
+  <si>
+    <t>Ievadi katra veikala PĀRDOTO GABALU KOPĀ par pēdējām 4 nedēļām</t>
+  </si>
+  <si>
+    <t>Aprēķins</t>
+  </si>
+  <si>
+    <t>Programma pati sadala 4 nedēļu kopējo daudzumu ar 4 un salīdzina ar pašreizējo nedēļu</t>
   </si>
   <si>
     <t>Produkta nosaukums</t>
@@ -111,13 +135,6 @@
     <t>Iepirkuma cena bez PVN</t>
   </si>
   <si>
-    <t xml:space="preserve">Biķernieku iela 21, Vidzemes priekšpilsēta, Rīga, LV-1039
-</t>
-  </si>
-  <si>
-    <t>Centra laukums 1, Ezere, Ezeres pagasts, LV-3891</t>
-  </si>
-  <si>
     <t>69VB2702492</t>
   </si>
   <si>
@@ -149,12 +166,6 @@
   </si>
   <si>
     <t>BOT_ALE</t>
-  </si>
-  <si>
-    <t>Grenctāle, Robežkontroles punkts, Brunavas pagasts, Bauskas novads, LV-3907</t>
-  </si>
-  <si>
-    <t>10.08–16.08.2026</t>
   </si>
 </sst>
 </file>
@@ -164,7 +175,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\€0.00"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -181,14 +192,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -197,46 +200,24 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
-      <charset val="186"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="186"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="186"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -272,41 +253,45 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{4390E113-8763-46C0-91A6-AAA207E39C35}"/>
-    <cellStyle name="Normal 2 15" xfId="2" xr:uid="{C005C09A-55E9-4DA5-BE3A-2653D1AC3D3F}"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 2 15" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -319,6 +304,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -608,214 +597,285 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:BO3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="15.7109375" customWidth="1"/>
+    <col min="1" max="2" width="22" style="10" customWidth="1"/>
+    <col min="3" max="3" width="55.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="22" style="10" customWidth="1"/>
+    <col min="7" max="22" width="16" style="10" customWidth="1"/>
+    <col min="23" max="67" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="173.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:67" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="H1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="7"/>
+      <c r="X1" s="7"/>
+      <c r="Y1" s="7"/>
+      <c r="Z1" s="7"/>
+      <c r="AA1" s="7"/>
+      <c r="AB1" s="7"/>
+      <c r="AC1" s="7"/>
+      <c r="AD1" s="7"/>
+      <c r="AE1" s="7"/>
+      <c r="AF1" s="7"/>
+      <c r="AG1" s="7"/>
+      <c r="AH1" s="7"/>
+      <c r="AI1" s="7"/>
+      <c r="AJ1" s="7"/>
+      <c r="AK1" s="7"/>
+      <c r="AL1" s="7"/>
+      <c r="AM1" s="7"/>
+      <c r="AN1" s="7"/>
+      <c r="AO1" s="7"/>
+      <c r="AP1" s="7"/>
+      <c r="AQ1" s="7"/>
+      <c r="AR1" s="7"/>
+      <c r="AS1" s="7"/>
+      <c r="AT1" s="7"/>
+      <c r="AU1" s="7"/>
+      <c r="AV1" s="7"/>
+      <c r="AW1" s="7"/>
+      <c r="AX1" s="7"/>
+      <c r="AY1" s="7"/>
+      <c r="AZ1" s="7"/>
+      <c r="BA1" s="7"/>
+      <c r="BB1" s="7"/>
+      <c r="BC1" s="7"/>
+      <c r="BD1" s="7"/>
+      <c r="BE1" s="7"/>
+      <c r="BF1" s="7"/>
+      <c r="BG1" s="7"/>
+      <c r="BH1" s="7"/>
+      <c r="BI1" s="7"/>
+      <c r="BJ1" s="7"/>
+      <c r="BK1" s="7"/>
+      <c r="BL1" s="7"/>
+      <c r="BM1" s="7"/>
+      <c r="BN1" s="7"/>
+      <c r="BO1" s="7"/>
+    </row>
+    <row r="2" spans="1:67" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="8">
+        <v>2</v>
+      </c>
+      <c r="H2" s="8">
+        <v>7</v>
+      </c>
+      <c r="I2" s="8">
+        <v>17</v>
+      </c>
+      <c r="J2" s="8">
+        <v>5</v>
+      </c>
+      <c r="K2" s="8">
+        <v>16</v>
+      </c>
+      <c r="L2" s="8">
+        <v>6</v>
+      </c>
+      <c r="M2" s="8">
+        <v>86</v>
+      </c>
+      <c r="N2" s="8">
         <v>1</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="O2" s="8">
+        <v>6</v>
+      </c>
+      <c r="P2" s="8">
         <v>2</v>
       </c>
-      <c r="G1" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="7" t="s">
+      <c r="Q2" s="8">
+        <v>38</v>
+      </c>
+      <c r="R2" s="8">
+        <v>13</v>
+      </c>
+      <c r="S2" s="8">
         <v>9</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="7" t="s">
+      <c r="T2" s="8">
         <v>11</v>
       </c>
-      <c r="L1" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="7" t="s">
+      <c r="U2" s="8">
+        <f>SUM(G2:T2)</f>
+        <v>219</v>
+      </c>
+      <c r="V2" s="9">
+        <f>AVERAGE(G2,H2,I2,J2,K2,L2,M2,N2,O2,P2,Q2,R2,S2,T2,U2)/4</f>
+        <v>7.3</v>
+      </c>
+      <c r="W2">
+        <f>U2/4</f>
+        <v>54.75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:67" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="R1" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="T1" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="U1" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" s="3">
-        <v>1</v>
-      </c>
-      <c r="H2" s="3">
-        <v>1</v>
-      </c>
-      <c r="I2" s="3">
-        <v>6</v>
-      </c>
-      <c r="J2" s="3">
-        <v>1</v>
-      </c>
-      <c r="K2" s="3">
-        <v>1</v>
-      </c>
-      <c r="L2" s="3">
-        <v>3</v>
-      </c>
-      <c r="M2" s="3">
-        <v>7</v>
-      </c>
-      <c r="N2" s="3">
-        <v>0</v>
-      </c>
-      <c r="O2" s="3">
-        <v>3</v>
-      </c>
-      <c r="P2" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>15</v>
-      </c>
-      <c r="R2" s="3">
-        <v>3</v>
-      </c>
-      <c r="S2" s="3">
-        <v>5</v>
-      </c>
-      <c r="T2" s="3">
-        <v>1</v>
-      </c>
-      <c r="U2" s="3">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>34</v>
+      <c r="B3" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="3">
-        <v>251</v>
-      </c>
-      <c r="H3" s="3">
-        <v>133</v>
-      </c>
-      <c r="I3" s="3">
-        <v>146</v>
-      </c>
-      <c r="J3" s="3">
-        <v>67</v>
-      </c>
-      <c r="K3" s="3">
-        <v>343</v>
-      </c>
-      <c r="L3" s="3">
-        <v>892</v>
-      </c>
-      <c r="M3" s="3">
-        <v>201</v>
-      </c>
-      <c r="N3" s="3">
-        <v>85</v>
-      </c>
-      <c r="O3" s="3">
-        <v>166</v>
-      </c>
-      <c r="P3" s="3">
-        <v>111</v>
-      </c>
-      <c r="Q3" s="3">
-        <v>306</v>
-      </c>
-      <c r="R3" s="3">
-        <v>133</v>
-      </c>
-      <c r="S3" s="3">
-        <v>347</v>
-      </c>
-      <c r="T3" s="3">
-        <v>205</v>
-      </c>
-      <c r="U3" s="3">
-        <v>3386</v>
+        <v>40</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="8">
+        <v>718</v>
+      </c>
+      <c r="H3" s="8">
+        <v>521</v>
+      </c>
+      <c r="I3" s="8">
+        <v>726</v>
+      </c>
+      <c r="J3" s="8">
+        <v>179</v>
+      </c>
+      <c r="K3" s="8">
+        <v>1126</v>
+      </c>
+      <c r="L3" s="8">
+        <v>3203</v>
+      </c>
+      <c r="M3" s="8">
+        <v>520</v>
+      </c>
+      <c r="N3" s="8">
+        <v>293</v>
+      </c>
+      <c r="O3" s="8">
+        <v>724</v>
+      </c>
+      <c r="P3" s="8">
+        <v>465</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>1061</v>
+      </c>
+      <c r="R3" s="8">
+        <v>421</v>
+      </c>
+      <c r="S3" s="8">
+        <v>1509</v>
+      </c>
+      <c r="T3" s="8">
+        <v>598</v>
+      </c>
+      <c r="U3" s="8">
+        <f>SUM(G3:T3)</f>
+        <v>12064</v>
+      </c>
+      <c r="V3" s="9">
+        <f>AVERAGE(G3,H3,I3,J3,K3,L3,M3,N3,O3,P3,Q3,R3,S3,T3,U3)/4</f>
+        <v>402.13333333333333</v>
+      </c>
+      <c r="W3">
+        <f>U3/4</f>
+        <v>3016</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:V1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA5A9427-354D-4482-A7AD-D1FC10775B5F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -825,52 +885,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="10"/>
+      <c r="A1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>24</v>
+      <c r="A4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="11">
+    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="3">
         <v>4.49</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="3">
         <v>1.66</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="11">
+    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="3">
         <v>1.0900000000000001</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="3">
         <v>0.72</v>
       </c>
     </row>

--- a/Book_previous.xlsx
+++ b/Book_previous.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gelsvalt-my.sharepoint.com/personal/u087_gelsva_lt/Documents/Desktop/python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="11_455FE02DEA73FC0327D0D3F114FB421ECD3234A9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CB058E2-DB7D-49DE-A53D-544D0901E3DD}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="11_455FE02DEA73FC0327D0D3F114FB421ECD3234A9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BD62EAA-47FA-4083-BD6D-7DECF67C0B13}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -135,15 +135,6 @@
     <t>Iepirkuma cena bez PVN</t>
   </si>
   <si>
-    <t>69VB2702492</t>
-  </si>
-  <si>
-    <t>8028277000563</t>
-  </si>
-  <si>
-    <t>Chiara Tuncis saulespuķu eļļā 80gx3</t>
-  </si>
-  <si>
     <t>FOOD</t>
   </si>
   <si>
@@ -153,19 +144,28 @@
     <t>PRESERV</t>
   </si>
   <si>
-    <t>LV014399</t>
-  </si>
-  <si>
-    <t>4750142004980</t>
-  </si>
-  <si>
-    <t>#Cēsu Premium pint alus can 0,568L 5%</t>
-  </si>
-  <si>
     <t>BEER</t>
   </si>
   <si>
     <t>BOT_ALE</t>
+  </si>
+  <si>
+    <t>CH1000645</t>
+  </si>
+  <si>
+    <t>9002859051753</t>
+  </si>
+  <si>
+    <t>Sardīnes saulespuķu eļļā 115g</t>
+  </si>
+  <si>
+    <t>LV014398</t>
+  </si>
+  <si>
+    <t>4750142005062</t>
+  </si>
+  <si>
+    <t>#Cēsu Brūža nefiltrets alus can 0,568L 5,4%</t>
   </si>
 </sst>
 </file>
@@ -306,10 +306,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -722,150 +718,150 @@
     </row>
     <row r="2" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="E2" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="F2" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>37</v>
-      </c>
       <c r="G2" s="8">
+        <v>4</v>
+      </c>
+      <c r="H2" s="8">
         <v>2</v>
       </c>
-      <c r="H2" s="8">
-        <v>7</v>
-      </c>
       <c r="I2" s="8">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J2" s="8">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="K2" s="8">
-        <v>16</v>
+        <v>446</v>
       </c>
       <c r="L2" s="8">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="M2" s="8">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="N2" s="8">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="O2" s="8">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="P2" s="8">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Q2" s="8">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="R2" s="8">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="S2" s="8">
+        <v>70</v>
+      </c>
+      <c r="T2" s="8">
         <v>9</v>
-      </c>
-      <c r="T2" s="8">
-        <v>11</v>
       </c>
       <c r="U2" s="8">
         <f>SUM(G2:T2)</f>
-        <v>219</v>
+        <v>884</v>
       </c>
       <c r="V2" s="9">
         <f>AVERAGE(G2,H2,I2,J2,K2,L2,M2,N2,O2,P2,Q2,R2,S2,T2,U2)/4</f>
-        <v>7.3</v>
+        <v>29.466666666666665</v>
       </c>
       <c r="W2">
         <f>U2/4</f>
-        <v>54.75</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>22</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G3" s="8">
-        <v>718</v>
+        <v>113</v>
       </c>
       <c r="H3" s="8">
-        <v>521</v>
+        <v>145</v>
       </c>
       <c r="I3" s="8">
-        <v>726</v>
+        <v>249</v>
       </c>
       <c r="J3" s="8">
-        <v>179</v>
+        <v>84</v>
       </c>
       <c r="K3" s="8">
-        <v>1126</v>
+        <v>140</v>
       </c>
       <c r="L3" s="8">
-        <v>3203</v>
+        <v>479</v>
       </c>
       <c r="M3" s="8">
-        <v>520</v>
+        <v>127</v>
       </c>
       <c r="N3" s="8">
-        <v>293</v>
+        <v>120</v>
       </c>
       <c r="O3" s="8">
-        <v>724</v>
+        <v>292</v>
       </c>
       <c r="P3" s="8">
-        <v>465</v>
+        <v>155</v>
       </c>
       <c r="Q3" s="8">
-        <v>1061</v>
+        <v>421</v>
       </c>
       <c r="R3" s="8">
-        <v>421</v>
+        <v>149</v>
       </c>
       <c r="S3" s="8">
-        <v>1509</v>
+        <v>402</v>
       </c>
       <c r="T3" s="8">
-        <v>598</v>
+        <v>149</v>
       </c>
       <c r="U3" s="8">
         <f>SUM(G3:T3)</f>
-        <v>12064</v>
+        <v>3025</v>
       </c>
       <c r="V3" s="9">
         <f>AVERAGE(G3,H3,I3,J3,K3,L3,M3,N3,O3,P3,Q3,R3,S3,T3,U3)/4</f>
-        <v>402.13333333333333</v>
+        <v>100.83333333333333</v>
       </c>
       <c r="W3">
         <f>U3/4</f>
-        <v>3016</v>
+        <v>756.25</v>
       </c>
     </row>
   </sheetData>
@@ -922,24 +918,24 @@
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B5" s="3">
-        <v>4.49</v>
+        <v>1.99</v>
       </c>
       <c r="C5" s="3">
-        <v>1.66</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B6" s="3">
-        <v>1.0900000000000001</v>
+        <v>1.19</v>
       </c>
       <c r="C6" s="3">
-        <v>0.72</v>
+        <v>0.86392000000000002</v>
       </c>
     </row>
   </sheetData>
